--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,14 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <strike val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -108,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -137,6 +145,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3167,7 +3187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3219,27 +3239,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Audited balance sheet / P&amp;L / ITR</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>GujRERA findoc</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Gujarat projects only</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Financial strength sub-metric currently scores None for every project. This would score it for GJ.</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Financial strength sub-metric currently scores None for every project. This would score it for GJ. RESOLVED 2026-08-28 for the single-project score (added to company_charter._HIGH_PRIORITY_DOC_KEYWORDS); the group-wide check (group_financial_disclosure.py) was widened 2026-09-09 to also cover West Bengal, Uttar Pradesh and Tamil Nadu -- though only Gujarat, Jharkhand, Haryana and West Bengal have a live-confirmed hit; UP and TN expose a searchable document list but have not produced one.</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3273,135 +3293,135 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>K-RERA defaulters list</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>K-RERA, observed</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Karnataka projects</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>No equivalent exists in any other authority. Direct red-flag input.</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>No equivalent exists in any other authority. Direct red-flag input. RESOLVED 2026-09-09: adapter_karnataka.fetch_default_projects / search_default_projects_by_promoter reads K-RERA's own "Default Project List" (/viewDefaultProjects, 2,991 rows), wired into litigation_sweep.state_order_sweep via its new karnataka_defaults param.</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>K-RERA projects under investigation</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>K-RERA, observed</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Karnataka projects</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Same -- a regulator-declared adverse signal.</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Same -- a regulator-declared adverse signal. ALREADY COVERED, not a real gap: K-RERA's "Complaints under process" register (COMPLAINT_DETAILS_PAGE) has been part of _ORDER_REGISTERS / search_all_orders_by_promoter since the "Wire the seven unused registers" commit -- this finding predates that wiring and was stale.</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>K-RERA cost incurred vs estimated</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>K-RERA detail page</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Karnataka projects</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Financial-strength scores None everywhere today. This is a direct, free input.</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Financial-strength scores None everywhere today. This is a direct, free input. RESOLVED 2026-08-28 (per docs/PAN_INDIA_PROGRESS.md): cost incurred/estimated and extension history now render in company_charter._append_project_cost_extension_section, unconditional for K-RERA projects.</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>K-RERA delay reasons + NOC expiry</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>K-RERA detail page</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Karnataka projects</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Promoter-declared delay reasons and lapsed-NOC tracking; no equivalent elsewhere.</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Promoter-declared delay reasons and lapsed-NOC tracking; no equivalent elsewhere. RESOLVED 2026-09-09: adapter_karnataka._parse_detail now reads Delay Reason plus TWO distinct NOC tables (obtained-at-all status, and separately an obtained NOC's own expiry/renewal), rendered in company_charter._append_project_delay_noc_section. NOC "expiry tracking" specifically was empty on every project checked live -- the table is real, just rarely populated.</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Maha Bhulekh card fields</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Free portal, extraction broken</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Maharashtra projects</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Owner, area, tenure, encumbrance and mutation are all ON the card and none reach the document.</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Owner, area, tenure, encumbrance and mutation are all ON the card and none reach the document. RESOLVED 2026-08-24 (per docs/PAN_INDIA_PROGRESS.md): run_cts_land_lookup -&gt; company_charter._append_cts_land_record_section.</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3425,7 +3445,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>An independent, free, party-named check on registrations against a property/CTS number or a specific document number -- CAPTCHA-gated but otherwise unauthenticated. search_by_document_number() is confirmed against a real pulled result: seller/purchaser names, full property description and the ACTUAL CONSIDERATION AMOUNT in one row, no further click needed -- a direct corroboration (or contradiction) of a promoter's declared land dealings that nothing else in this pipeline checks independently. search_by_property() is also built and, confirmed live chasing a real Pune search, turned out to need THREE separate regions (mumbai/rest_of_maharashtra/urban), each its own field ids and cascade shape -- the landing page's default tab covers only the two Mumbai districts, not the whole state as it first appeared. A locality can sit in either the rural or urban region depending on how it was annexed: Pune's Market Yard (Gulatekadi) is under 'urban', not the rural taluka/village list a human would try first, and guessing wrong doesn't error -- it just returns a real but unrelated village list. All three regions' form mechanics are confirmed live end-to-end up to the CAPTCHA gate; the RESULT TABLE'S OWN SHAPE for search_by_property is still not confirmed against a real row for any of them, unlike document-number search. Also carries an integrated CERSAI cross-search on the same page, not yet driven by either function. A standalone script, run by a human, same as every other CAPTCHA-gated tool here -- not called from the automated Charter pipeline.</t>
+          <t>An independent, free, party-named check on registrations against a property/CTS number or a specific document number -- CAPTCHA-gated but otherwise unauthenticated. search_by_document_number() is confirmed against a real pulled result: seller/purchaser names, full property description and the ACTUAL CONSIDERATION AMOUNT in one row, no further click needed -- a direct corroboration (or contradiction) of a promoter's declared land dealings that nothing else in this pipeline checks independently. search_by_property() is also built and, confirmed live chasing a real Pune search, turned out to need THREE separate regions (mumbai/rest_of_maharashtra/urban), each its own field ids and cascade shape -- the landing page's default tab covers only the two Mumbai districts, not the whole state as it first appeared. A locality can sit in either the rural or urban region depending on how it was annexed: Pune's Market Yard (Gulatekadi) is under 'urban', not the rural taluka/village list a human would try first, and guessing wrong doesn't error -- it just returns a real but unrelated village list. All three regions' form mechanics are confirmed live end-to-end up to the CAPTCHA gate; the RESULT TABLE'S OWN SHAPE for search_by_property is still not confirmed against a real row for any of them, unlike document-number search. Also carries an integrated CERSAI cross-search on the same page, not yet driven by either function. A standalone script, run by a human, same as every other CAPTCHA-gated tool here -- not called from the automated Charter pipeline. DELIBERATELY NOT AUTOMATED, not a gap: CAPTCHA-gated and human-in-the-loop by design, same reasoning as cts_resolve.py/ts_rera_client.py -- wiring it into the unattended pipeline would need redesigning around the CAPTCHA, not just calling the existing script.</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -3435,270 +3455,297 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>JHARERA audited balance sheet + 3 years ITR</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>adapter_jharkhand.py document library (labelled, downloaded)</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>Jharkhand projects</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Same gap as GujRERA's findoc block: the financial-strength sub-metric scores None for every project regardless of state. This would score it for JH too.</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Same gap as GujRERA's findoc block: the financial-strength sub-metric scores None for every project regardless of state. This would score it for JH too. RESOLVED 2026-08-28 for the single-project score (same fix as row 5 above); the group-wide check was widened 2026-09-09 -- see row 5's note.</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>JHARERA rejected + surrendered registration lists</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>REJECTED_LIST / SURRENDERED_LIST, imported into the adapter but never fetched</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Jharkhand projects</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>A rejected or surrendered registration is diligence material with no equivalent on MahaRERA. The URLs are already wired into the import list; nothing calls them yet.</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>A rejected or surrendered registration is diligence material with no equivalent on MahaRERA. The URLs are already wired into the import list; nothing calls them yet. RESOLVED 2026-09-09: adapter_jharkhand.fetch_rejected_projects / fetch_surrendered_projects (parse_rejected_or_surrendered_register), wired into group_enforcement.sweep.</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>WBRERA defaulters list</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>adapter_westbengal.fetch_defaulters() -- written, unwired, untested live</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>West Bengal projects</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>17 rejected/defaulting applications keyed by name -- a cheap, direct red-flag input. The parser exists but is called from nowhere in acquire() or the litigation sweep.</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>17 rejected/defaulting applications keyed by name -- a cheap, direct red-flag input. The parser exists but is called from nowhere in acquire() or the litigation sweep. RESOLVED 2026-09-09: wired into group_enforcement.sweep (confirmed live at 18 rows, not the 17 this finding was originally written against -- the portal has grown since). Its register names the PROJECT, not the promoter, so a hit is weaker evidence than this pass's other registers.</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>UP-RERA de-registered/defaulter list</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>adapter_uttarpradesh.fetch_defaulters() -- written, unwired, live-verified 2026-08-26 (72 rows)</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Uttar Pradesh projects</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Named by promoter outright -- ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED is on it. Reachable only via an ASP.NET postback, not a plain URL, which is why nothing had fetched it before.</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Named by promoter outright -- ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED is on it. Reachable only via an ASP.NET postback, not a plain URL, which is why nothing had fetched it before. RESOLVED (pre-existing): wired into group_enforcement.sweep by the "Wire the seven unused registers and two financial sources into the Charter" commit, before this row was last reviewed.</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>HARERA cancelled/defaulter projects</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>adapter_haryana.fetch_defaulter_projects() -- written, unwired, live-verified 2026-08-26 (23 Panchkula + 5 Gurugram)</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Haryana projects</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Distinct from the already-imported LAPSED_PROJECTS URL, which is validity expiry, not an authority action -- conflating the two would understate lapsed rows as defaults or vice versa.</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Distinct from the already-imported LAPSED_PROJECTS URL, which is validity expiry, not an authority action -- conflating the two would understate lapsed rows as defaults or vice versa. RESOLVED (pre-existing): same commit as row 16.</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>TNRERA penalty register</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>adapter_tamilnadu.fetch_penalty_notices() -- written, unwired, live-verified 2026-08-26 (147 rows across Building + Layout)</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Tamil Nadu projects</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Names promoter, project and the penalty amount levied -- TNRERA's own closest equivalent to a defaulters list, titled 'Penalty' rather than that.</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Names promoter, project and the penalty amount levied -- TNRERA's own closest equivalent to a defaulters list, titled 'Penalty' rather than that. RESOLVED (pre-existing): same commit as row 16.</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>TNRERA unregistered-project enforcement PDFs</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>adapter_tamilnadu.search_enforcement_lists_by_name() -- written, unwired, live-verified 2026-08-26 (35 + 1,502 rows, native-text PDFs, no OCR needed)</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>Tamil Nadu projects/promoters</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>The show-cause and personal-use-caution lists, now actually searchable by name rather than merely linked as static PDFs. Ceiling is real, not fixable in code: both cover UNREGISTERED sites, never a registered project under suo-moto scrutiny.</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>The show-cause and personal-use-caution lists, now actually searchable by name rather than merely linked as static PDFs. Ceiling is real, not fixable in code: both cover UNREGISTERED sites, never a registered project under suo-moto scrutiny. RESOLVED (pre-existing): same commit as row 16.</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Delhi-RERA suo-moto register</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>adapter_delhi.parse_suo_moto_register() -- written, unwired, live-verified 2026-08-26 (1,797 rows)</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Delhi projects</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Names a Respondent/Promoter and project per row -- the clearest 'projects under investigation' signal found on any of the four newest states, and Delhi otherwise has no per-project record at all.</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Names a Respondent/Promoter and project per row -- the clearest 'projects under investigation' signal found on any of the four newest states, and Delhi otherwise has no per-project record at all. RESOLVED (pre-existing): same commit as row 16.</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Delhi-RERA execution register</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>adapter_delhi.parse_execution_register() -- written, unwired, live-verified 2026-08-26 (7,493 rows)</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>Delhi projects</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Orders referred for enforcement because the promoter (named as Judgement Debtor) did not comply -- the authority's own closest equivalent to a defaulters list.</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Orders referred for enforcement because the promoter (named as Judgement Debtor) did not comply -- the authority's own closest equivalent to a defaulters list. RESOLVED (pre-existing): same commit as row 16.</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Delhi-RERA Appellate Tribunal (REAT) register, WITH party names</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>adapter_delhi.build_appeal_party_index() / search_appeals_by_party() -- written, unwired, live-verified 2026-08-26 (437/505 rows named, 481 PDFs OCR'd)</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Delhi projects</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>The register itself names no party -- not linked from any Delhi-RERA page either, found only by web search -- but every row links a scanned judgement PDF whose own case caption does. OCRing just the PDFs' first pages (PyMuPDF native text, confirmed zero on every sample -- Tesseract fallback) turned an unsearchable register into one where search_appeals_by_party('Parsvnath') returns 27 real hits. The only gaps are the authority's own 63 broken PDF links and 5 older (2021-2022) PDFs in a caption shape not yet recognised.</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>The register itself names no party -- not linked from any Delhi-RERA page either, found only by web search -- but every row links a scanned judgement PDF whose own case caption does. OCRing just the PDFs' first pages (PyMuPDF native text, confirmed zero on every sample -- Tesseract fallback) turned an unsearchable register into one where search_appeals_by_party('Parsvnath') returns 27 real hits. The only gaps are the authority's own 63 broken PDF links and 5 older (2021-2022) PDFs in a caption shape not yet recognised. RESOLVED (pre-existing): same commit as row 16.</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>K-RERA Revenue Recovery Certificates</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>adapter_karnataka.fetch_revenue_recovery_list() -- found and wired 2026-09-09</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Karnataka projects</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Promoters against whom an unpaid penalty has escalated to an RRC -- K-RERA's strongest enforcement signal short of a criminal referral, and a real PROMOTER NAME column unlike most registers here. RESOLVED on discovery 2026-09-09: wired into litigation_sweep.state_order_sweep via its new karnataka_revenue_recovery param (2,603 rows confirmed live).</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -16,8 +16,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A - RERA by authority'!$A$4:$M$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B - CTS land records'!$A$4:$F$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C - CIN corporate'!$A$4:$G$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D - Available but unused'!$A$4:$E$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C - CIN corporate'!$A$4:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D - Available but unused'!$A$4:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,14 +52,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <strike val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -116,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -145,18 +137,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -540,7 +520,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regenerated 2026-08-31 by build_data_coverage.py</t>
+          <t>Regenerated 2026-09-23 by build_data_coverage.py</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2510,7 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Audited live 2026-09-01 with a REAL result, not just a reachable form. Two search modes, both free and CAPTCHA-gated (confirmed via DOM inspection, not just a page-text guess): 'Property Details' (Year -&gt; District -&gt; Village/Area, an autocomplete text field paired with a dropdown -&gt; Survey/CTS/Milkat/Gat/Plot No.; a name-based search is also offered once a property number is entered) and 'Document Number' (Registration Type [eFiling/eRegistration/Regular/iSarita 2.0] -&gt; District, all 37 -- this mode is genuinely statewide, not Mumbai-only -&gt; SRO -&gt; Year -&gt; Doc No.). Document Number/SRO Mumbai 9 (Andheri)/2024/#100 returned a real registered Leave &amp; License agreement dated 03/01/2024 -- Seller/Lessor 'Ramesh Babulal Shah', Purchaser/Lessee 'M/s Matushri Impex' (through partner Ramesh T. Bhalani), full property description (Bandra Kurla Complex premises, CTS No. 4207) AND consideration (monthly rent Rs 44,100 plus Rs 5,29,200 advance for the first 12 months) -- all present in the RESULT LIST ROW ITSELF, no further click needed. Each row also carries an 'IndexII' button (a further postback, __doPostBack('RegistrationGrid','indexII$0')) documented in the site's own User Guide as opening a fuller Index II view in a separate window -- present and clickable, but its own content was NOT captured this pass (the popup did not materialize in this environment), so that specific view stays unconfirmed rather than assumed. A real, stated limitation from the site's own FAQ: Power of Attorney and Will deeds are NOT available in search results. Mumbai city and Suburban districts go back to 1985; 'selected offices' elsewhere now reach back before the earlier 2002 baseline too, per the site's own notice.</t>
+          <t>Audited live 2026-09-01 with a REAL result, not just a reachable form. Two search modes, both free and CAPTCHA-gated (confirmed via DOM inspection, not just a page-text guess): 'Property Details' (Year -&gt; District -&gt; Village/Area, an autocomplete text field paired with a dropdown -&gt; Survey/CTS/Milkat/Gat/Plot No.; a name-based search is also offered once a property number is entered) and 'Document Number' (Registration Type [eFiling/eRegistration/Regular/iSarita 2.0] -&gt; District, all 37 -- this mode is genuinely statewide, not Mumbai-only -&gt; SRO -&gt; Year -&gt; Doc No.). Document Number/SRO Mumbai 9 (Andheri)/2024/#100 returned a real registered Leave &amp; License agreement dated 03/01/2024 -- Seller/Lessor 'Ramesh Babulal Shah', Purchaser/Lessee 'M/s Matushri Impex' (through partner Ramesh T. Bhalani), full property description (Bandra Kurla Complex premises, CTS No. 4207) AND consideration (monthly rent Rs 44,100 plus Rs 5,29,200 advance for the first 12 months) -- all present in the RESULT LIST ROW ITSELF, no further click needed. Each row also carries an 'IndexII' button (a further postback, __doPostBack('RegistrationGrid','indexII$0')) documented in the site's own User Guide as opening a fuller Index II view in a separate window -- present and clickable, but its own content was NOT captured this pass (the popup did not materialize in this environment), so that specific view stays unconfirmed rather than assumed. A real, stated limitation from the site's own FAQ: Power of Attorney and Will deeds are NOT available in search results. Mumbai city and Suburban districts go back to 1985; 'selected offices' elsewhere now reach back before the earlier 2002 baseline too, per the site's own notice. WIRED IN 2026-09-15 (run_igr_registered_deed_check): document-number search only, asked directly of a human at the terminal (district/SRO/year/doc-no, no candidate list) since a document number is either already in hand or not knowable at all; search_by_property() stays unwired since its result shape is still unconfirmed against a real row.</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3171,8 +3151,82 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>NCLT Case Status (direct tribunal query)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>NCLT e-filing Case Status portal, party-name search</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Free + CAPTCHA</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>confirmed-live</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>nclt_check</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>WIRED IN 2026-09-15. A DIRECT party-name query against the tribunal's own portal -- distinct from _safe_group_litigation's indirect Indian Kanoon name search just above. CAPTCHA-gated (one solve) and human-in-the-loop: only runs when a human is actually at this terminal, never headlessly. Mumbai Bench only; the other 15 benches nationwide are not searched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Bombay High Court Case Status (direct eCourts query)</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Bombay HC eCourts Case Status, party-name search</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Free + CAPTCHA</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>confirmed-live</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>bombay_hc_check</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>WIRED IN 2026-09-15. A DIRECT party-name query, Original Side + Appellate Side (the two Bombay-city benches) across the last 5 registration years -- 10 separate CAPTCHA-gated lookups, since the portal requires a mandatory Registration Year per search. The other 5 benches (Aurangabad/Nagpur/Kolhapur/Goa/Special Court) are not searched by default. Used to also require an explicit human consent prompt before running, on top of the terminal check, given the 10x cost; removed 2026-09-23 once a human being present for every run of this pipeline was no longer in question.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G14"/>
+  <autoFilter ref="A4:G16"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -3187,7 +3241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3239,27 +3293,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Audited balance sheet / P&amp;L / ITR</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>GujRERA findoc</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Gujarat projects only</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Financial strength sub-metric currently scores None for every project. This would score it for GJ. RESOLVED 2026-08-28 for the single-project score (added to company_charter._HIGH_PRIORITY_DOC_KEYWORDS); the group-wide check (group_financial_disclosure.py) was widened 2026-09-09 to also cover West Bengal, Uttar Pradesh and Tamil Nadu -- though only Gujarat, Jharkhand, Haryana and West Bengal have a live-confirmed hit; UP and TN expose a searchable document list but have not produced one.</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Financial strength sub-metric currently scores None for every project. This would score it for GJ.</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3293,135 +3347,135 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>K-RERA defaulters list</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>K-RERA, observed</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Karnataka projects</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>No equivalent exists in any other authority. Direct red-flag input. RESOLVED 2026-09-09: adapter_karnataka.fetch_default_projects / search_default_projects_by_promoter reads K-RERA's own "Default Project List" (/viewDefaultProjects, 2,991 rows), wired into litigation_sweep.state_order_sweep via its new karnataka_defaults param.</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>No equivalent exists in any other authority. Direct red-flag input.</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>K-RERA projects under investigation</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>K-RERA, observed</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Karnataka projects</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Same -- a regulator-declared adverse signal. ALREADY COVERED, not a real gap: K-RERA's "Complaints under process" register (COMPLAINT_DETAILS_PAGE) has been part of _ORDER_REGISTERS / search_all_orders_by_promoter since the "Wire the seven unused registers" commit -- this finding predates that wiring and was stale.</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Same -- a regulator-declared adverse signal.</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>K-RERA cost incurred vs estimated</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>K-RERA detail page</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Karnataka projects</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Financial-strength scores None everywhere today. This is a direct, free input. RESOLVED 2026-08-28 (per docs/PAN_INDIA_PROGRESS.md): cost incurred/estimated and extension history now render in company_charter._append_project_cost_extension_section, unconditional for K-RERA projects.</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Financial-strength scores None everywhere today. This is a direct, free input.</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>K-RERA delay reasons + NOC expiry</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>K-RERA detail page</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Karnataka projects</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Promoter-declared delay reasons and lapsed-NOC tracking; no equivalent elsewhere. RESOLVED 2026-09-09: adapter_karnataka._parse_detail now reads Delay Reason plus TWO distinct NOC tables (obtained-at-all status, and separately an obtained NOC's own expiry/renewal), rendered in company_charter._append_project_delay_noc_section. NOC "expiry tracking" specifically was empty on every project checked live -- the table is real, just rarely populated.</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Promoter-declared delay reasons and lapsed-NOC tracking; no equivalent elsewhere.</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Maha Bhulekh card fields</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Free portal, extraction broken</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Maharashtra projects</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Owner, area, tenure, encumbrance and mutation are all ON the card and none reach the document. RESOLVED 2026-08-24 (per docs/PAN_INDIA_PROGRESS.md): run_cts_land_lookup -&gt; company_charter._append_cts_land_record_section.</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Owner, area, tenure, encumbrance and mutation are all ON the card and none reach the document.</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3430,22 +3484,22 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>IGR Maharashtra registered-deed search</t>
+          <t>JHARERA audited balance sheet + 3 years ITR</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>igr_maharashtra_search.py -- BUILT 2026-09-01, human-in-the-loop like up_captcha_search.py/cts_resolve.py, not wired into run_company_charter()</t>
+          <t>adapter_jharkhand.py document library (labelled, downloaded)</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Maharashtra projects</t>
+          <t>Jharkhand projects</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>An independent, free, party-named check on registrations against a property/CTS number or a specific document number -- CAPTCHA-gated but otherwise unauthenticated. search_by_document_number() is confirmed against a real pulled result: seller/purchaser names, full property description and the ACTUAL CONSIDERATION AMOUNT in one row, no further click needed -- a direct corroboration (or contradiction) of a promoter's declared land dealings that nothing else in this pipeline checks independently. search_by_property() is also built and, confirmed live chasing a real Pune search, turned out to need THREE separate regions (mumbai/rest_of_maharashtra/urban), each its own field ids and cascade shape -- the landing page's default tab covers only the two Mumbai districts, not the whole state as it first appeared. A locality can sit in either the rural or urban region depending on how it was annexed: Pune's Market Yard (Gulatekadi) is under 'urban', not the rural taluka/village list a human would try first, and guessing wrong doesn't error -- it just returns a real but unrelated village list. All three regions' form mechanics are confirmed live end-to-end up to the CAPTCHA gate; the RESULT TABLE'S OWN SHAPE for search_by_property is still not confirmed against a real row for any of them, unlike document-number search. Also carries an integrated CERSAI cross-search on the same page, not yet driven by either function. A standalone script, run by a human, same as every other CAPTCHA-gated tool here -- not called from the automated Charter pipeline. DELIBERATELY NOT AUTOMATED, not a gap: CAPTCHA-gated and human-in-the-loop by design, same reasoning as cts_resolve.py/ts_rera_client.py -- wiring it into the unattended pipeline would need redesigning around the CAPTCHA, not just calling the existing script.</t>
+          <t>Same gap as GujRERA's findoc block: the financial-strength sub-metric scores None for every project regardless of state. This would score it for JH too.</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -3455,304 +3509,250 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>JHARERA audited balance sheet + 3 years ITR</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>adapter_jharkhand.py document library (labelled, downloaded)</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>JHARERA rejected + surrendered registration lists</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>REJECTED_LIST / SURRENDERED_LIST, imported into the adapter but never fetched</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Jharkhand projects</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Same gap as GujRERA's findoc block: the financial-strength sub-metric scores None for every project regardless of state. This would score it for JH too. RESOLVED 2026-08-28 for the single-project score (same fix as row 5 above); the group-wide check was widened 2026-09-09 -- see row 5's note.</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>A rejected or surrendered registration is diligence material with no equivalent on MahaRERA. The URLs are already wired into the import list; nothing calls them yet.</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>WBRERA defaulters list</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>adapter_westbengal.fetch_defaulters() -- written, unwired, untested live</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>West Bengal projects</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>17 rejected/defaulting applications keyed by name -- a cheap, direct red-flag input. The parser exists but is called from nowhere in acquire() or the litigation sweep.</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>UP-RERA de-registered/defaulter list</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>adapter_uttarpradesh.fetch_defaulters() -- written, unwired, live-verified 2026-08-26 (72 rows)</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh projects</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Named by promoter outright -- ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED is on it. Reachable only via an ASP.NET postback, not a plain URL, which is why nothing had fetched it before.</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>JHARERA rejected + surrendered registration lists</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>REJECTED_LIST / SURRENDERED_LIST, imported into the adapter but never fetched</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Jharkhand projects</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>A rejected or surrendered registration is diligence material with no equivalent on MahaRERA. The URLs are already wired into the import list; nothing calls them yet. RESOLVED 2026-09-09: adapter_jharkhand.fetch_rejected_projects / fetch_surrendered_projects (parse_rejected_or_surrendered_register), wired into group_enforcement.sweep.</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>HARERA cancelled/defaulter projects</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>adapter_haryana.fetch_defaulter_projects() -- written, unwired, live-verified 2026-08-26 (23 Panchkula + 5 Gurugram)</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Haryana projects</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Distinct from the already-imported LAPSED_PROJECTS URL, which is validity expiry, not an authority action -- conflating the two would understate lapsed rows as defaults or vice versa.</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>WBRERA defaulters list</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>adapter_westbengal.fetch_defaulters() -- written, unwired, untested live</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>West Bengal projects</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>17 rejected/defaulting applications keyed by name -- a cheap, direct red-flag input. The parser exists but is called from nowhere in acquire() or the litigation sweep. RESOLVED 2026-09-09: wired into group_enforcement.sweep (confirmed live at 18 rows, not the 17 this finding was originally written against -- the portal has grown since). Its register names the PROJECT, not the promoter, so a hit is weaker evidence than this pass's other registers.</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>TNRERA penalty register</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>adapter_tamilnadu.fetch_penalty_notices() -- written, unwired, live-verified 2026-08-26 (147 rows across Building + Layout)</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Tamil Nadu projects</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Names promoter, project and the penalty amount levied -- TNRERA's own closest equivalent to a defaulters list, titled 'Penalty' rather than that.</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>UP-RERA de-registered/defaulter list</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>adapter_uttarpradesh.fetch_defaulters() -- written, unwired, live-verified 2026-08-26 (72 rows)</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh projects</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Named by promoter outright -- ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED is on it. Reachable only via an ASP.NET postback, not a plain URL, which is why nothing had fetched it before. RESOLVED (pre-existing): wired into group_enforcement.sweep by the "Wire the seven unused registers and two financial sources into the Charter" commit, before this row was last reviewed.</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>TNRERA unregistered-project enforcement PDFs</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>adapter_tamilnadu.search_enforcement_lists_by_name() -- written, unwired, live-verified 2026-08-26 (35 + 1,502 rows, native-text PDFs, no OCR needed)</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Tamil Nadu projects/promoters</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>The show-cause and personal-use-caution lists, now actually searchable by name rather than merely linked as static PDFs. Ceiling is real, not fixable in code: both cover UNREGISTERED sites, never a registered project under suo-moto scrutiny.</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Delhi-RERA suo-moto register</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>adapter_delhi.parse_suo_moto_register() -- written, unwired, live-verified 2026-08-26 (1,797 rows)</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Delhi projects</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Names a Respondent/Promoter and project per row -- the clearest 'projects under investigation' signal found on any of the four newest states, and Delhi otherwise has no per-project record at all.</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>HARERA cancelled/defaulter projects</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>adapter_haryana.fetch_defaulter_projects() -- written, unwired, live-verified 2026-08-26 (23 Panchkula + 5 Gurugram)</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>Haryana projects</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Distinct from the already-imported LAPSED_PROJECTS URL, which is validity expiry, not an authority action -- conflating the two would understate lapsed rows as defaults or vice versa. RESOLVED (pre-existing): same commit as row 16.</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Delhi-RERA execution register</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>adapter_delhi.parse_execution_register() -- written, unwired, live-verified 2026-08-26 (7,493 rows)</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Delhi projects</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Orders referred for enforcement because the promoter (named as Judgement Debtor) did not comply -- the authority's own closest equivalent to a defaulters list.</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>TNRERA penalty register</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>adapter_tamilnadu.fetch_penalty_notices() -- written, unwired, live-verified 2026-08-26 (147 rows across Building + Layout)</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>Tamil Nadu projects</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Names promoter, project and the penalty amount levied -- TNRERA's own closest equivalent to a defaulters list, titled 'Penalty' rather than that. RESOLVED (pre-existing): same commit as row 16.</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>TNRERA unregistered-project enforcement PDFs</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>adapter_tamilnadu.search_enforcement_lists_by_name() -- written, unwired, live-verified 2026-08-26 (35 + 1,502 rows, native-text PDFs, no OCR needed)</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>Tamil Nadu projects/promoters</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>The show-cause and personal-use-caution lists, now actually searchable by name rather than merely linked as static PDFs. Ceiling is real, not fixable in code: both cover UNREGISTERED sites, never a registered project under suo-moto scrutiny. RESOLVED (pre-existing): same commit as row 16.</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Delhi-RERA suo-moto register</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>adapter_delhi.parse_suo_moto_register() -- written, unwired, live-verified 2026-08-26 (1,797 rows)</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Delhi-RERA Appellate Tribunal (REAT) register, WITH party names</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>adapter_delhi.build_appeal_party_index() / search_appeals_by_party() -- written, unwired, live-verified 2026-08-26 (437/505 rows named, 481 PDFs OCR'd)</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Delhi projects</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Names a Respondent/Promoter and project per row -- the clearest 'projects under investigation' signal found on any of the four newest states, and Delhi otherwise has no per-project record at all. RESOLVED (pre-existing): same commit as row 16.</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>The register itself names no party -- not linked from any Delhi-RERA page either, found only by web search -- but every row links a scanned judgement PDF whose own case caption does. OCRing just the PDFs' first pages (PyMuPDF native text, confirmed zero on every sample -- Tesseract fallback) turned an unsearchable register into one where search_appeals_by_party('Parsvnath') returns 27 real hits. The only gaps are the authority's own 63 broken PDF links and 5 older (2021-2022) PDFs in a caption shape not yet recognised.</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Delhi-RERA execution register</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>adapter_delhi.parse_execution_register() -- written, unwired, live-verified 2026-08-26 (7,493 rows)</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Delhi projects</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Orders referred for enforcement because the promoter (named as Judgement Debtor) did not comply -- the authority's own closest equivalent to a defaulters list. RESOLVED (pre-existing): same commit as row 16.</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Delhi-RERA Appellate Tribunal (REAT) register, WITH party names</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>adapter_delhi.build_appeal_party_index() / search_appeals_by_party() -- written, unwired, live-verified 2026-08-26 (437/505 rows named, 481 PDFs OCR'd)</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Delhi projects</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>The register itself names no party -- not linked from any Delhi-RERA page either, found only by web search -- but every row links a scanned judgement PDF whose own case caption does. OCRing just the PDFs' first pages (PyMuPDF native text, confirmed zero on every sample -- Tesseract fallback) turned an unsearchable register into one where search_appeals_by_party('Parsvnath') returns 27 real hits. The only gaps are the authority's own 63 broken PDF links and 5 older (2021-2022) PDFs in a caption shape not yet recognised. RESOLVED (pre-existing): same commit as row 16.</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>K-RERA Revenue Recovery Certificates</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>adapter_karnataka.fetch_revenue_recovery_list() -- found and wired 2026-09-09</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Karnataka projects</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>Promoters against whom an unpaid penalty has escalated to an RRC -- K-RERA's strongest enforcement signal short of a criminal referral, and a real PROMOTER NAME column unlike most registers here. RESOLVED on discovery 2026-09-09: wired into litigation_sweep.state_order_sweep via its new karnataka_revenue_recovery param (2,603 rows confirmed live).</t>
-        </is>
-      </c>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:E22"/>
+  <autoFilter ref="A4:E21"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-23 by build_data_coverage.py</t>
+          <t>Regenerated 2026-10-19 by build_data_coverage.py</t>
         </is>
       </c>
     </row>
@@ -729,6 +729,13 @@
       <c r="A34" s="3" t="inlineStr">
         <is>
           <t>18. IGR Maharashtra e-Search -- Sheet B's last two 'observed' rows, closed live 2026-09-01 with a REAL pulled result, not just a reachable form. freesearchigrservice.maharashtra.gov.in offers two free, CAPTCHA-gated search modes (Property Details: Year/District/Village-or-Area/Survey-CTS-Milkat-Gat-Plot No.; Document Number: Registration Type/District, all 37, genuinely statewide/SRO/Year/Doc No.). Document Number/SRO Mumbai 9 (Andheri)/2024/#100 returned a real registered Leave &amp; License agreement -- seller and purchaser named, full property description, AND the actual consideration (Rs 44,100/month plus Rs 5,29,200 advance) -- all in the result row itself, no extra click. Genuine limitation found along the way, from the site's own FAQ: Power of Attorney and Will deeds are excluded from search entirely. Equitable mortgages share the identical mechanism and evidence -- a Notice of Intimation is just one more possible deed-name value, not a separately filterable category -- but no live mortgage example was actually pulled this pass, so that row confirms the channel, not a specific instance. Also found: the page's own 'CERSAI Search' button is an integrated postback on this same portal, not an external redirect. Added to Sheet D as a new high-value, unbuilt finding -- nothing in this pipeline calls this portal yet, and it is the only independent, party-named check on a promoter's registered dealings this pipeline has found for Maharashtra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>19. CAPTCHA autosolve went pipeline-wide 2026-10-15, Claude-vision-only. CapSolver and every human-wait fallback were REMOVED entirely from every CAPTCHA-gated portal this pipeline touches, by explicit user instruction applied to ALL portals at once, not just the one in front of us -- CapSolver could not reliably solve IGR's case-sensitive mixed-case CAPTCHA even once Claude vision worked, and a human-wait loop is dead time with no human present by design. Confirmed live, each now solving its own CAPTCHA by default (an explicit *_CAPTCHA_AUTOSOLVE=0 env var opts OUT, nothing opts in): MahaRERA, IGR (both the Document Number and Property Details search modes, including the Index II popup fetch), Mahabhumi's property-card lookup, TS-RERA's (Telangana) party-name search, UP-RERA's project search, and UP-REAT's appeals search -- the last of which moves this sheet's Appeals-register cell for UP-RERA from Partial to Yes, since the one thing holding it at Partial was the human CAPTCHA cost. GST (PAN-&gt;GSTIN intake) autosolve code is ready but not fully proven -- the portal was WAF-blocked during testing and live verification was explicitly deferred. NCLT and Bombay HC ALSO now autosolve by default in the code on disk, which is recorded in Sheet C -- but flagged there deliberately: a separate 2026-10-15 conversation had the user ask three times to extend autosolve to exactly these two portals, got declined each time on this pipeline's own standing rule against ever completing or bypassing a CAPTCHA, and the user's recorded decision at the time was to leave their human-wait code untouched. The code and CLAUDE.md now say otherwise; which one is current was put back to the user while regenerating this sheet, and the answer was to document the code as it stands. Separately, a real correctness bug was fixed 2026-10-13: MahaRERA's order search could silently return the authority's generic unfiltered recent-orders page as if it were a filtered promoter search, fabricating ~1,640 'matches' across 57 names with zero genuine hits among them -- any group-litigation output cached before that fix is suspect. And one gap stayed open on purpose rather than being quietly fixed: Maha Bhulekh's structured owner/area/tenure/encumbrance/mutation fields still parse to {} even with the CAPTCHA no longer in the way -- OCR of the embedded card image is the only route confirmed to actually carry that content, not the DOM parser this sheet's Maha Bhulekh rows describe.</t>
         </is>
       </c>
     </row>
@@ -1414,9 +1421,9 @@
           <t>Not published</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -1441,7 +1448,7 @@
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t>TNRERA is Not published, audited live 2026-08-26: a Tamil Nadu Real Estate Appellate Tribunal (TNREAT) DOES exist, distinct from the authority -- it has its own domain, tnreat.tn.gov.in, linked from TNRERA's own homepage -- but its public page carries no case search, cause list or judgment register at all, only a sign-in and a virtual-meeting-report link. Not a stub of the authority's own order registers: a genuinely separate body that simply publishes nothing searchable to the public. UP-RERA is Partial: its own Appellate Tribunal (UP-REAT) runs a live judgement search at efilingreat.up.gov.in/upreat/judgement.php with a free-text party-name field, CAPTCHA-gated. CONFIRMED LIVE 2026-08-26 the gate is passable, not just present: up_captcha_search.py opens a real browser, a human reads and solves the CAPTCHA, and the search genuinely runs -- tested against BALAJIMAHIMA INFRATECH PRIVATE LIMITED, which returned a clean 'No Data Found' in a real results table (Sr.No/Filing No./Case No./Case Title/Registration Date/Action), not an error or an empty page. Stays Partial rather than Yes because every search still costs one human CAPTCHA solve -- real and working, but not unattended. HARERA is Yes: the Haryana Real Estate Appellate Tribunal is served off HARERA's own domain (haryanarera.gov.in/admincontrol/judgements/3), a plain GET with no CAPTCHA -- 2,779 rows of Appeal No. / Appellant Name / Respondent Name / Date of Decision, confirmed promoter-searchable. Delhi-RERA is now Yes, upgraded from Partial 2026-08-26: REAT Delhi (shared with the UT of Chandigarh, not linked from any Delhi-RERA page, found only by web search) publishes a live 505-row register that names no party in its own columns -- but every row links a scanned judgement PDF, and REAT's own case captions name the Appellant and Respondent on the PDF's first page. states/adapter_delhi.py's build_appeal_party_index() downloads and OCRs (PyMuPDF native text first, Tesseract fallback -- confirmed live that every PDF sampled is a scan, zero native text) just that first page across all 481 distinct order PDFs behind the 505 rows, extracting both party names by the caption's own structure rather than guessing at fixed columns. Confirmed live 2026-08-26: 437/505 rows (87%) now carry a real party name -- searching 'Parsvnath' returns 27 real hits, e.g. 'Bimal Kumar &amp; Ors. vs M/s Parsvnath Landmark Developers Pvt. Ltd.' Of the 68 rows that don't, 63 are the AUTHORITY'S OWN register linking a PDF that 404s (a genuine broken link on their side, confirmed directly), and only 5 PDFs (12 rows, all 2021-2022 vintage) use a caption shape the parser doesn't recognise. search_appeals_by_party() is the promoter-facing search this unlocks, still unwired into acquire().</t>
+          <t>TNRERA is Not published, audited live 2026-08-26: a Tamil Nadu Real Estate Appellate Tribunal (TNREAT) DOES exist, distinct from the authority -- it has its own domain, tnreat.tn.gov.in, linked from TNRERA's own homepage -- but its public page carries no case search, cause list or judgment register at all, only a sign-in and a virtual-meeting-report link. Not a stub of the authority's own order registers: a genuinely separate body that simply publishes nothing searchable to the public. UP-RERA is Partial: its own Appellate Tribunal (UP-REAT) runs a live judgement search at efilingreat.up.gov.in/upreat/judgement.php with a free-text party-name field, CAPTCHA-gated. CONFIRMED LIVE 2026-08-26 the gate is passable, not just present: up_captcha_search.py opens a real browser, a human reads and solves the CAPTCHA, and the search genuinely runs -- tested against BALAJIMAHIMA INFRATECH PRIVATE LIMITED, which returned a clean 'No Data Found' in a real results table (Sr.No/Filing No./Case No./Case Title/Registration Date/Action), not an error or an empty page. UPGRADED to Yes 2026-10-15: the one thing keeping this Partial -- every search costing one human CAPTCHA solve, not unattended -- no longer holds. solve_up_reat_captcha (Claude vision) now solves this page's own CAPTCHA by default, confirmed live on attempt 1/8, with the portal's exact rejection text ('Captch Value is incorrect/Empty, kindly try again', the site's own typo) used as the retry signal; a live search found 20 real litigation rows for a Parsvnath Developers query. HARERA is Yes: the Haryana Real Estate Appellate Tribunal is served off HARERA's own domain (haryanarera.gov.in/admincontrol/judgements/3), a plain GET with no CAPTCHA -- 2,779 rows of Appeal No. / Appellant Name / Respondent Name / Date of Decision, confirmed promoter-searchable. Delhi-RERA is now Yes, upgraded from Partial 2026-08-26: REAT Delhi (shared with the UT of Chandigarh, not linked from any Delhi-RERA page, found only by web search) publishes a live 505-row register that names no party in its own columns -- but every row links a scanned judgement PDF, and REAT's own case captions name the Appellant and Respondent on the PDF's first page. states/adapter_delhi.py's build_appeal_party_index() downloads and OCRs (PyMuPDF native text first, Tesseract fallback -- confirmed live that every PDF sampled is a scan, zero native text) just that first page across all 481 distinct order PDFs behind the 505 rows, extracting both party names by the caption's own structure rather than guessing at fixed columns. Confirmed live 2026-08-26: 437/505 rows (87%) now carry a real party name -- searching 'Parsvnath' returns 27 real hits, e.g. 'Bimal Kumar &amp; Ors. vs M/s Parsvnath Landmark Developers Pvt. Ltd.' Of the 68 rows that don't, 63 are the AUTHORITY'S OWN register linking a PDF that 404s (a genuine broken link on their side, confirmed directly), and only 5 PDFs (12 rows, all 2021-2022 vintage) use a caption shape the parser doesn't recognise. search_appeals_by_party() is the promoter-facing search this unlocks, still unwired into acquire().</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1515,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>K-RERA now reads FIVE promoter-keyed registers (order search, authority orders, AO orders, interim orders, complaints under process) -- 15,600+ rows including a penalty table naming the violation, section and amount. JHARERA's judgement/order register is searchable by promoter, though a share of rows name both parties in one unsplit column and are therefore invisible to that search. WBRERA's order register names no party at all; the join runs through its cause lists instead, so its coverage note matters more than its row count.</t>
+          <t>K-RERA now reads FIVE promoter-keyed registers (order search, authority orders, AO orders, interim orders, complaints under process) -- 15,600+ rows including a penalty table naming the violation, section and amount. JHARERA's judgement/order register is searchable by promoter, though a share of rows name both parties in one unsplit column and are therefore invisible to that search. WBRERA's order register names no party at all; the join runs through its cause lists instead, so its coverage note matters more than its row count. MahaRERA's own order search had a false-positive bug FIXED 2026-10-13 (test_maharera_orders_filter.py): a documented fallback GET could land on the authority's generic, unfiltered recent-orders listing, which passed the existing results-marker check and returned it as if it were a filtered promoter search -- one real run returned ~1,640 'matching' rows across 57 promoter/ group-entity names with only 113 distinct orders total and zero of them actually naming any of the 57 promoters. Fixed with a loose token-overlap check against each row's own respondent_name (excluding generic suffixes like 'private'/'limited'/'builders'); any group-litigation output cached before that fix should be treated as suspect and re-run, not trusted.</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2347,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free + CAPTCHA (autosolved)</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -2350,7 +2357,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>PRESENT on the free card. Extraction is what is broken -- the parser looks for ZaubaCorp's li.row pattern, but the card is an HTML table.</t>
+          <t>PRESENT on the free card. Extraction is what is broken -- the parser looks for ZaubaCorp's li.row pattern, but the card is an HTML table. REVISED 2026-10-15: the CAPTCHA that gates the final submit is no longer the blocker -- mahabhumi.py's fetch_property_card() now solves it via Claude vision by default (MAHABHUMI_CAPTCHA_AUTOSOLVE=1 unless set to 0), confirmed live end-to-end for CTS 862 / Lower Parel, Mumbai City (accepted on attempt 2/8). But the DOM-based structured-field parsing this row's finding describes still returns {} on every real lookup -- unchanged by the autosolve work, and not something it was meant to fix. The only route actually confirmed to carry owner/area/tenure/encumbrance/mutation content end to end is OCR of the embedded card image (1,241 chars of real Marathi/English text recovered on the confirming run), not the structured parser this row's 'Partial' status assumes will eventually be fixed.</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2379,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free + CAPTCHA (autosolved)</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -2382,7 +2389,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Present on the card; same extraction gap.</t>
+          <t>Present on the card; same extraction gap, same 2026-10-15 CAPTCHA-autosolve and OCR-route update as the Owner / holder name row above.</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2411,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free + CAPTCHA (autosolved)</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -2414,7 +2421,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Only source for this field -- Index II does not carry occupancy class.</t>
+          <t>Only source for this field -- Index II does not carry occupancy class. Same 2026-10-15 CAPTCHA-autosolve and OCR-route update as the Owner / holder name row above.</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2443,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free + CAPTCHA (autosolved)</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -2446,7 +2453,7 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Present as a labelled row.</t>
+          <t>Present as a labelled row. Same 2026-10-15 CAPTCHA-autosolve and OCR-route update as the Owner / holder name row above.</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2475,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free + CAPTCHA (autosolved)</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -2478,7 +2485,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Full dated table with mutation numbers, present on the card.</t>
+          <t>Full dated table with mutation numbers, present on the card. Same 2026-10-15 CAPTCHA-autosolve and OCR-route update as the Owner / holder name row above.</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2517,7 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Audited live 2026-09-01 with a REAL result, not just a reachable form. Two search modes, both free and CAPTCHA-gated (confirmed via DOM inspection, not just a page-text guess): 'Property Details' (Year -&gt; District -&gt; Village/Area, an autocomplete text field paired with a dropdown -&gt; Survey/CTS/Milkat/Gat/Plot No.; a name-based search is also offered once a property number is entered) and 'Document Number' (Registration Type [eFiling/eRegistration/Regular/iSarita 2.0] -&gt; District, all 37 -- this mode is genuinely statewide, not Mumbai-only -&gt; SRO -&gt; Year -&gt; Doc No.). Document Number/SRO Mumbai 9 (Andheri)/2024/#100 returned a real registered Leave &amp; License agreement dated 03/01/2024 -- Seller/Lessor 'Ramesh Babulal Shah', Purchaser/Lessee 'M/s Matushri Impex' (through partner Ramesh T. Bhalani), full property description (Bandra Kurla Complex premises, CTS No. 4207) AND consideration (monthly rent Rs 44,100 plus Rs 5,29,200 advance for the first 12 months) -- all present in the RESULT LIST ROW ITSELF, no further click needed. Each row also carries an 'IndexII' button (a further postback, __doPostBack('RegistrationGrid','indexII$0')) documented in the site's own User Guide as opening a fuller Index II view in a separate window -- present and clickable, but its own content was NOT captured this pass (the popup did not materialize in this environment), so that specific view stays unconfirmed rather than assumed. A real, stated limitation from the site's own FAQ: Power of Attorney and Will deeds are NOT available in search results. Mumbai city and Suburban districts go back to 1985; 'selected offices' elsewhere now reach back before the earlier 2002 baseline too, per the site's own notice. WIRED IN 2026-09-15 (run_igr_registered_deed_check): document-number search only, asked directly of a human at the terminal (district/SRO/year/doc-no, no candidate list) since a document number is either already in hand or not knowable at all; search_by_property() stays unwired since its result shape is still unconfirmed against a real row.</t>
+          <t>Audited live 2026-09-01 with a REAL result, not just a reachable form. Two search modes, both free and CAPTCHA-gated (confirmed via DOM inspection, not just a page-text guess): 'Property Details' (Year -&gt; District -&gt; Village/Area, an autocomplete text field paired with a dropdown -&gt; Survey/CTS/Milkat/Gat/Plot No.; a name-based search is also offered once a property number is entered) and 'Document Number' (Registration Type [eFiling/eRegistration/Regular/iSarita 2.0] -&gt; District, all 37 -- this mode is genuinely statewide, not Mumbai-only -&gt; SRO -&gt; Year -&gt; Doc No.). Document Number/SRO Mumbai 9 (Andheri)/2024/#100 returned a real registered Leave &amp; License agreement dated 03/01/2024 -- Seller/Lessor 'Ramesh Babulal Shah', Purchaser/Lessee 'M/s Matushri Impex' (through partner Ramesh T. Bhalani), full property description (Bandra Kurla Complex premises, CTS No. 4207) AND consideration (monthly rent Rs 44,100 plus Rs 5,29,200 advance for the first 12 months) -- all present in the RESULT LIST ROW ITSELF, no further click needed. Each row also carries an 'IndexII' button (a further postback, __doPostBack('RegistrationGrid','indexII$0')) documented in the site's own User Guide as opening a fuller Index II view in a separate window -- present and clickable, but its own content was NOT captured this pass (the popup did not materialize in this environment), so that specific view stays unconfirmed rather than assumed. A real, stated limitation from the site's own FAQ: Power of Attorney and Will deeds are NOT available in search results. Mumbai city and Suburban districts go back to 1985; 'selected offices' elsewhere now reach back before the earlier 2002 baseline too, per the site's own notice. WIRED IN 2026-09-15 (run_igr_registered_deed_check): document-number search only, asked directly of a human at the terminal (district/SRO/year/doc-no, no candidate list) since a document number is either already in hand or not knowable at all; search_by_property() stays unwired since its result shape is still unconfirmed against a real row. REVISED 2026-10-15: search_by_property() IS now proven live end-to-end, not merely unconfirmed -- both IGR search modes solve their own CAPTCHA via Claude vision by default (no CapSolver, no human-wait fallback left anywhere in the module), fixed a stale ASP.NET __EVENTTARGET bug and a pager-row misparse that were causing silent false negatives, and a confirmed GENUINE backend non-determinism (byte-identical POST data, different results) was mitigated with a 3-attempt retry. A full 2020-2026 year-by-year sweep against one real Mumbai property (Parel, Property No. 10) returned real documents for every single year, 66 rows total, zero genuine negatives once retried enough times. One real parser gap remains open, NOT fixed: 5 of those 66 rows use a second Index II page layout the 14-field parser doesn't recognise (deed type 'Notice of intimation regarding mortgage by way of deposit of Title Deed'), so numeric/date/party fields blank out on those specific rows rather than misreading them -- needs a fresh live sample of that template to fix properly.</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3176,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Free + CAPTCHA</t>
+          <t>Free + CAPTCHA (autosolved)</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -3184,7 +3191,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>WIRED IN 2026-09-15. A DIRECT party-name query against the tribunal's own portal -- distinct from _safe_group_litigation's indirect Indian Kanoon name search just above. CAPTCHA-gated (one solve) and human-in-the-loop: only runs when a human is actually at this terminal, never headlessly. Mumbai Bench only; the other 15 benches nationwide are not searched.</t>
+          <t>WIRED IN 2026-09-15. A DIRECT party-name query against the tribunal's own portal -- distinct from _safe_group_litigation's indirect Indian Kanoon name search just above. REVISED 2026-10-15: no longer human-in-the-loop. nclt_search.py now solves its own CAPTCHA via Claude vision by default (NCLT_CAPTCHA_AUTOSOLVE=1 unless explicitly set to 0), retrying only on the portal's own explicit CAPTCHA-rejection text; there is no human-wait fallback left in the module. This capability sits directly inside this pipeline's own Prohibited-actions rule against completing or bypassing a CAPTCHA -- an earlier session explicitly declined to extend autosolve here on that basis and the code was meant to stay human-wait; it currently does not, and the project's own CLAUDE.md now documents autosolve as the intended design. Recorded here as what the code on disk actually does, per the user's explicit instruction when this discrepancy was raised. Mumbai Bench only; the other 15 benches nationwide are not searched.</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3213,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Free + CAPTCHA</t>
+          <t>Free + CAPTCHA (autosolved)</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -3221,7 +3228,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>WIRED IN 2026-09-15. A DIRECT party-name query, Original Side + Appellate Side (the two Bombay-city benches) across the last 5 registration years -- 10 separate CAPTCHA-gated lookups, since the portal requires a mandatory Registration Year per search. The other 5 benches (Aurangabad/Nagpur/Kolhapur/Goa/Special Court) are not searched by default. Used to also require an explicit human consent prompt before running, on top of the terminal check, given the 10x cost; removed 2026-09-23 once a human being present for every run of this pipeline was no longer in question.</t>
+          <t>WIRED IN 2026-09-15. A DIRECT party-name query, Original Side + Appellate Side (the two Bombay-city benches) across the last 5 registration years -- 10 separate CAPTCHA-gated lookups, since the portal requires a mandatory Registration Year per search. The other 5 benches (Aurangabad/Nagpur/Kolhapur/Goa/Special Court) are not searched by default. Used to also require an explicit human consent prompt before running, on top of the terminal check, given the 10x cost; removed 2026-09-23 once a human being present for every run of this pipeline was no longer in question. REVISED 2026-10-15, same basis and same caveat as the NCLT row above: bombay_hc_search.py now solves its own CAPTCHA via Claude vision by default (BOMBAY_HC_CAPTCHA_AUTOSOLVE=1 unless set to 0) across all 10 lookups, with no human-wait fallback remaining.</t>
         </is>
       </c>
     </row>

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regenerated 2026-10-19 by build_data_coverage.py</t>
+          <t>Regenerated 2026-10-22 by build_data_coverage.py</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Free portal, extraction broken</t>
+          <t>Free portal, now has an OCR fallback for image-only cards</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Owner, area, tenure, encumbrance and mutation are all ON the card and none reach the document.</t>
+          <t>WIRED 2026-10-22: confirmed live that a property with no digitized attribute data on file renders as a single scanned JPEG even with English selected (parse_property_card correctly returns {} on that page -- there is no markup to read, not a parser bug). mahabhumi._fields_from_ocr_text() now OCRs the cropped card image itself (not the noisy full-page screenshot) and extracts labelled fields from the OCR text as `ocr_fields`, kept separate from the DOM-parsed `fields` so a caller can tell a table read from a lower-confidence scan guess. Verified against two real saved captures with digitized cards (full fields/mutations) and one real image-only capture (ocr_fields now the only route in).</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>adapter_uttarpradesh.fetch_defaulters() -- written, unwired, live-verified 2026-08-26 (72 rows)</t>
+          <t>adapter_uttarpradesh.fetch_defaulters() -- WIRED 2026-10-22 via UttarPradeshAdapter._defaulter_check(), live-verified 2026-08-26 and again on wiring (72 rows)</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Named by promoter outright -- ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED is on it. Reachable only via an ASP.NET postback, not a plain URL, which is why nothing had fetched it before.</t>
+          <t>Named by promoter outright -- ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED is on it (3 matching rows, re-confirmed live). Runs unconditionally on every UP-RERA acquire(): one homepage GET plus one ASP.NET postback for the whole state's register, not a per-project cost.</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>adapter_delhi.parse_suo_moto_register() -- written, unwired, live-verified 2026-08-26 (1,797 rows)</t>
+          <t>adapter_delhi.parse_suo_moto_register() -- WIRED 2026-10-22 via DelhiAdapter._suo_moto(), live-verified 2026-08-26 and again on wiring (1,781 rows)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Names a Respondent/Promoter and project per row -- the clearest 'projects under investigation' signal found on any of the four newest states, and Delhi otherwise has no per-project record at all.</t>
+          <t>Names a Respondent/Promoter and project per row -- the clearest 'projects under investigation' signal found on any of the four newest states, and Delhi otherwise has no per-project record at all. Runs unconditionally: one GET for the whole register, same cost shape as the complaint register sweep already in this adapter. Surfaced as category_data['suo_moto_investigations']; not yet mapped to a Charter facts field (still '(unmapped)' in Sheet A).</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>adapter_delhi.build_appeal_party_index() / search_appeals_by_party() -- written, unwired, live-verified 2026-08-26 (437/505 rows named, 481 PDFs OCR'd)</t>
+          <t>adapter_delhi.build_appeal_party_index() / search_appeals_by_party() -- WIRED 2026-10-22 via DelhiAdapter._reat_appeals(), live-verified 2026-08-26 (437/505 rows named, 481 PDFs OCR'd)</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>The register itself names no party -- not linked from any Delhi-RERA page either, found only by web search -- but every row links a scanned judgement PDF whose own case caption does. OCRing just the PDFs' first pages (PyMuPDF native text, confirmed zero on every sample -- Tesseract fallback) turned an unsearchable register into one where search_appeals_by_party('Parsvnath') returns 27 real hits. The only gaps are the authority's own 63 broken PDF links and 5 older (2021-2022) PDFs in a caption shape not yet recognised.</t>
+          <t>The register itself names no party -- not linked from any Delhi-RERA page either, found only by web search -- but every row links a scanned judgement PDF whose own case caption does. OCRing just the PDFs' first pages (PyMuPDF native text, confirmed zero on every sample -- Tesseract fallback) turned an unsearchable register into one where search_appeals_by_party('Parsvnath') returns 27 real hits. The only gaps are the authority's own 63 broken PDF links and 5 older (2021-2022) PDFs in a caption shape not yet recognised. OFF BY DEFAULT even though wired: 481 PDFs is too expensive to fetch+OCR on every Delhi-RERA acquire() call, so it only runs with DELHI_REAT_SWEEP=1, caching each PDF's OCR text to &lt;output_dir&gt;/_reat_pdf_cache so a repeat sweep only pays for PDFs not seen before. A run without the flag set gets an explicit 'not swept' note, never a silent clean record.</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -3523,7 +3523,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>REJECTED_LIST / SURRENDERED_LIST, imported into the adapter but never fetched</t>
+          <t>REJECTED_LIST / SURRENDERED_LIST -- WIRED 2026-10-22 via JharkhandAdapter._rejected_or_surrendered_check(), live-verified on wiring (13 rows: 10 rejected + 3 surrendered)</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>A rejected or surrendered registration is diligence material with no equivalent on MahaRERA. The URLs are already wired into the import list; nothing calls them yet.</t>
+          <t>A rejected or surrendered registration is diligence material with no equivalent on MahaRERA. Runs unconditionally on every JHARERA acquire(): two cheap GETs for the whole state's registers, not a per-project cost.</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>adapter_westbengal.fetch_defaulters() -- written, unwired, untested live</t>
+          <t>adapter_westbengal.fetch_defaulters() -- WIRED 2026-10-22 via WestBengalAdapter._defaulter_check(), live-verified on wiring (18 rows)</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>17 rejected/defaulting applications keyed by name -- a cheap, direct red-flag input. The parser exists but is called from nowhere in acquire() or the litigation sweep.</t>
+          <t>A cheap, direct red-flag input. CORRECTED ON WIRING 2026-10-22: the register's own 'name' column is the PROJECT's name, not a promoter name -- there is no promoter field on this register at all, confirmed live. So this matches on the resolved project's own name, not promoter_name the way every other defaulter check in this pipeline does, and a hit says nothing about the promoter's other projects.</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>adapter_haryana.fetch_defaulter_projects() -- written, unwired, live-verified 2026-08-26 (23 Panchkula + 5 Gurugram)</t>
+          <t>adapter_haryana.fetch_defaulter_projects() -- WIRED 2026-10-22 via HaryanaAdapter._defaulter_check(), live-verified 2026-08-26 and again on wiring (23 Panchkula + 5 Gurugram)</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Distinct from the already-imported LAPSED_PROJECTS URL, which is validity expiry, not an authority action -- conflating the two would understate lapsed rows as defaults or vice versa.</t>
+          <t>Distinct from the already-imported LAPSED_PROJECTS URL, which is validity expiry, not an authority action -- conflating the two would understate lapsed rows as defaults or vice versa. Only the resolved project's OWN bench is checked per acquire() call; a promoter active on both benches under the same name would need both swept, left to the group-enforcement pass rather than a single-project lookup.</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>adapter_tamilnadu.fetch_penalty_notices() -- written, unwired, live-verified 2026-08-26 (147 rows across Building + Layout)</t>
+          <t>adapter_tamilnadu.fetch_penalty_notices() -- WIRED 2026-10-22 via TamilNaduAdapter._penalty_check(), live-verified 2026-08-26 and again on wiring (146 rows across Building + Layout)</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Names promoter, project and the penalty amount levied -- TNRERA's own closest equivalent to a defaulters list, titled 'Penalty' rather than that.</t>
+          <t>Names promoter, project and the penalty amount levied -- TNRERA's own closest equivalent to a defaulters list, titled 'Penalty' rather than that. Runs unconditionally: two GETs (Building + Layout) on every TNRERA acquire().</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>adapter_tamilnadu.search_enforcement_lists_by_name() -- written, unwired, live-verified 2026-08-26 (35 + 1,502 rows, native-text PDFs, no OCR needed)</t>
+          <t>adapter_tamilnadu.search_enforcement_lists_by_name() -- WIRED 2026-10-22 via TamilNaduAdapter._enforcement_check(), live-verified 2026-08-26 and again on wiring (35 + 1,502 rows, native-text PDFs, no OCR needed)</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>The show-cause and personal-use-caution lists, now actually searchable by name rather than merely linked as static PDFs. Ceiling is real, not fixable in code: both cover UNREGISTERED sites, never a registered project under suo-moto scrutiny.</t>
+          <t>The show-cause and personal-use-caution lists, now actually searchable by name rather than merely linked as static PDFs. Ceiling is real, not fixable in code: both cover UNREGISTERED sites, never a registered project under suo-moto scrutiny, so a hit is evidence about the PROMOTER, not this project. Runs unconditionally, though the personal-use caution PDF is 118 pages and noticeably slower than every other per-promoter check in this adapter.</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>adapter_delhi.parse_execution_register() -- written, unwired, live-verified 2026-08-26 (7,493 rows)</t>
+          <t>adapter_delhi.parse_execution_register() -- WIRED 2026-10-22 via DelhiAdapter._execution_register(), live-verified 2026-08-26 and again on wiring (5,921 rows)</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Orders referred for enforcement because the promoter (named as Judgement Debtor) did not comply -- the authority's own closest equivalent to a defaulters list.</t>
+          <t>Orders referred for enforcement because the promoter (named as Judgement Debtor) did not comply -- the authority's own closest equivalent to a defaulters list. Runs unconditionally: one GET for the whole register.</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A - RERA by authority'!$A$4:$M$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B - CTS land records'!$A$4:$F$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C - CIN corporate'!$A$4:$G$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D - Available but unused'!$A$4:$E$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D - Available but unused'!$A$4:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1875,41 +1875,41 @@
           <t>Not published</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
           <t>(unmapped)</t>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>K-RERA /viewDefaultProjects -- observed, not yet built. JHARERA's REJECTED and SURRENDERED registers are the closest equivalent: their URLs are imported into the adapter but nothing fetches them yet. WBRERA's defaulters list (17 rejected/defaulting applications by name) IS parsed by adapter_westbengal.fetch_defaulters(), but that function is called from nowhere in acquire() or the litigation sweep -- written, untested against a live page, and unused. TNRERA is Yes, audited live 2026-08-26: https://rera.tn.gov.in/building/online/penalty and .../layout/online/penalty are live, unpaginated pages naming the promoter, address, project and penalty levied -- 1 row on Building (TNRERA/PBF/0092/2025, M/S. VIKAS MANTRA PROPERTIES &amp; INFRASTRUCTURE PRIVATE LIMITED, Rs 20,10,940, 13-02-2025) and 146 on Layout. Titled 'Penalty', not 'Defaulters' or 'Black List' -- no register under either of those names was found, and no separate revoked/cancelled-registration list exists. An unwired parser (parse_penalty_register / fetch_penalty_notices) was added to states/adapter_tamilnadu.py, mirroring adapter_westbengal.fetch_defaulters(). UP-RERA is Yes: https://www.up-rera.in/DefaulterList (reachable only via the homepage's DE-REGISTERED PROJECTS postback, not a plain link) serves a live 72-row register -- reg. no., project name suffixed '(De-Registered Project)' or '(Defaulter Project)', district, promoter -- e.g. UPRERAPRJ7090, ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED. An unwired fetch_defaulters() was added to states/adapter_uttarpradesh.py. HARERA is Yes: /admincontrol/cancelled_projects/{bench} (menu label 'Defaulter/ Cancelled/ Suspended/ Abeyance Projects') is a distinct, live register -- 23 Panchkula + 5 Gurugram rows -- confirmed DIFFERENT from /admincontrol/lapsed_projects/{bench} (319 + 234 rows), which is only registrations whose validity date has passed, not a defaulter finding; both got unwired parsers in states/adapter_haryana.py. Delhi-RERA is Partial: the authority never uses the word 'defaulter', but courtview/ExecutionInOrderJudgementsAuthorityInfo -- 7,493 live rows of orders referred for enforcement because the promoter ('Judgement Debtor') did not comply -- is the closest real equivalent; got an unwired parser in states/adapter_delhi.py.</t>
+          <t>K-RERA /viewDefaultProjects -- CONFIRMED LIVE 2026-09-09 (2,991 rows, clean REGISTRATION NO / PROMOTER / PROJECT / DISTRICT columns), WIRED into KarnatakaAdapter.acquire() 2026-10-22 (previously only reachable via litigation_sweep.py's group sweep). JHARERA's REJECTED and SURRENDERED registers (13 rows combined) are the closest equivalent, WIRED 2026-10-22 via JharkhandAdapter._rejected_or_surrendered_check(). WBRERA's defaulters list (18 rows) is WIRED 2026-10-22 via WestBengalAdapter._defaulter_check() -- note it matches on PROJECT name, not promoter, since the register carries no promoter field at all. TNRERA is Yes, audited live 2026-08-26: https://rera.tn.gov.in/building/online/penalty and .../layout/online/penalty are live, unpaginated pages naming the promoter, address, project and penalty levied -- 1 row on Building (TNRERA/PBF/0092/2025, M/S. VIKAS MANTRA PROPERTIES &amp; INFRASTRUCTURE PRIVATE LIMITED, Rs 20,10,940, 13-02-2025) and 146 on Layout. Titled 'Penalty', not 'Defaulters' or 'Black List' -- no register under either of those names was found, and no separate revoked/cancelled-registration list exists. An unwired parser (parse_penalty_register / fetch_penalty_notices) was added to states/adapter_tamilnadu.py, mirroring adapter_westbengal.fetch_defaulters(). UP-RERA is Yes: https://www.up-rera.in/DefaulterList (reachable only via the homepage's DE-REGISTERED PROJECTS postback, not a plain link) serves a live 72-row register -- reg. no., project name suffixed '(De-Registered Project)' or '(Defaulter Project)', district, promoter -- e.g. UPRERAPRJ7090, ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED. An unwired fetch_defaulters() was added to states/adapter_uttarpradesh.py. HARERA is Yes: /admincontrol/cancelled_projects/{bench} (menu label 'Defaulter/ Cancelled/ Suspended/ Abeyance Projects') is a distinct, live register -- 23 Panchkula + 5 Gurugram rows -- confirmed DIFFERENT from /admincontrol/lapsed_projects/{bench} (319 + 234 rows), which is only registrations whose validity date has passed, not a defaulter finding; both got unwired parsers in states/adapter_haryana.py. Delhi-RERA is Partial: the authority never uses the word 'defaulter', but courtview/ExecutionInOrderJudgementsAuthorityInfo -- 7,493 live rows of orders referred for enforcement because the promoter ('Judgement Debtor') did not comply -- is the closest real equivalent; got an unwired parser in states/adapter_delhi.py.</t>
         </is>
       </c>
     </row>
@@ -1942,31 +1942,31 @@
           <t>Not published</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>Not published</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Not published</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
           <t>Not published</t>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>K-RERA /unregProjectList -- observed, not yet built. TNRERA stays Partial, but 'static (non-searchable)' is fixed as of 2026-08-26: both PDFs are NATIVE TEXT (confirmed live, zero OCR needed, unlike Delhi-RERA's REAT scans) and adapter_tamilnadu.py's parse_enforcement_pdf()/search_enforcement_lists_by_name() reads them with pdfplumber's table extraction -- 35 rows off the 5-page SCN list, 1,502 off the 118-page caution list, confirmed live end-to-end (searching 'Sivakaminathan' returns the real row). What did NOT change, because it is a finding about the authority's publication rather than a scraping gap: neither list covers a REGISTERED project under suo-moto scrutiny, only the unregistered-building enforcement pipeline -- 'Show Cause Notice issued for levy of penalty for non registration' and a 'Public Caution Notice' of buildings claimed as personal-use and therefore left unregistered. UP-RERA stays Partial for the opposite reason: the three adjacent registers (Abeyance, NCLT, Withdrawn Registration) named in the earlier audit are REAL pages, but their data loads via a WebService1.asmx POST that returned HTTP 500 on every parameter tried, including a real browser driving the page's own default (empty-parameter) call -- confirmed live 2026-08-26 this is the AUTHORITY'S OWN backend failing, not a request-shaping problem on this end, so nothing was built against a data source that cannot currently be read at all. HARERA is Not published: the only relevant menu item, 'Suo Motu (Projects) Cause List', is a hearing-schedule generator requiring a specific date and a CAPTCHA, not a browsable register; the only visible trace of suo-moto outcomes is inside HREAT's judgement text (case numbers containing 'MT' for Motu). Delhi-RERA is Yes: courtview/SuoMotoCases is a live, promoter-named, 1,797-row register of the authority's own-motion notices and orders -- the clearest 'projects under investigation' register found on any of the four new states; got an unwired parser in states/adapter_delhi.py.</t>
+          <t>K-RERA /unregProjectList -- genuinely never fetched before 2026-10-22. CONFIRMED LIVE: 1,050 rows, clean Project Name / Promoter Name / Status / Corporate Address / Published Date columns, Status carrying the authority's own finding (e.g. 'No Reply from Promoter'). WIRED the same day via KarnatakaAdapter._investigation_check(). TNRERA stays Partial, but 'static (non-searchable)' is fixed as of 2026-08-26: both PDFs are NATIVE TEXT (confirmed live, zero OCR needed, unlike Delhi-RERA's REAT scans) and adapter_tamilnadu.py's parse_enforcement_pdf()/search_enforcement_lists_by_name() reads them with pdfplumber's table extraction -- 35 rows off the 5-page SCN list, 1,502 off the 118-page caution list, confirmed live end-to-end (searching 'Sivakaminathan' returns the real row). What did NOT change, because it is a finding about the authority's publication rather than a scraping gap: neither list covers a REGISTERED project under suo-moto scrutiny, only the unregistered-building enforcement pipeline -- 'Show Cause Notice issued for levy of penalty for non registration' and a 'Public Caution Notice' of buildings claimed as personal-use and therefore left unregistered. UP-RERA stays Partial for the opposite reason: the three adjacent registers (Abeyance, NCLT, Withdrawn Registration) named in the earlier audit are REAL pages, but their data loads via a WebService1.asmx POST that returned HTTP 500 on every parameter tried, including a real browser driving the page's own default (empty-parameter) call -- confirmed live 2026-08-26 this is the AUTHORITY'S OWN backend failing, not a request-shaping problem on this end, so nothing was built against a data source that cannot currently be read at all. HARERA is Not published: the only relevant menu item, 'Suo Motu (Projects) Cause List', is a hearing-schedule generator requiring a specific date and a CAPTCHA, not a browsable register; the only visible trace of suo-moto outcomes is inside HREAT's judgement text (case numbers containing 'MT' for Motu). Delhi-RERA is Yes: courtview/SuoMotoCases is a live, promoter-named, 1,797-row register of the authority's own-motion notices and orders -- the clearest 'projects under investigation' register found on any of the four new states; got an unwired parser in states/adapter_delhi.py.</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>GujRERA findoc</t>
+          <t>GujRERA findoc -- WIRED 2026-10-22 via GujaratAdapter._financial_statements() / company_charter.financial_statements_from_documents()</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Financial strength sub-metric currently scores None for every project. This would score it for GJ.</t>
+          <t>PARTIALLY CLOSED: a P&amp;L statement's revenue/profit/financial-year figures are now extracted (same-line OCR matching only, confirmed live) and cited as evidence against the Financial Strength sub-metric's reason text -- but the sub-metric's score itself still stays None for every project. SCOPED DOWN ON PURPOSE: confirmed live against real saved documents that OCR of a Balance Sheet collapses its table structure badly (a total can land several lines away from its own label, with nothing left to say which belongs to which), so net worth/total debt -- the actual ratios this sub-metric scores -- are deliberately never extracted, to avoid a silently wrong number. Also confirmed live: a file labelled 'AHPL BALANCE SHEET 19-20.pdf' turned out to be an unrelated Gazette of India notification, not a financial statement at all -- extraction goes by the document's own text, never trusts the label.</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>K-RERA, observed</t>
+          <t>adapter_karnataka.fetch_default_projects() / search_default_projects_by_promoter() -- WIRED 2026-10-22 via KarnatakaAdapter._defaulter_check(), live-verified 2026-09-09 and again on wiring</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>No equivalent exists in any other authority. Direct red-flag input.</t>
+          <t>No equivalent exists in any other authority. Direct red-flag input. CORRECTED 2026-10-22: this row previously said 'observed, not yet built', but the fetch/parse/dedup logic (2,991-row state-wide register) was already built and tested on 2026-09-09 -- only wired to litigation_sweep.py's promoter-level group sweep, not this adapter's own per-project output. Now also surfaced per-project as category_data['defaulter_check'].</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>K-RERA, observed</t>
+          <t>adapter_karnataka.fetch_unregistered_investigation_list() / search_unregistered_investigations_by_promoter() -- WIRED 2026-10-22 via KarnatakaAdapter._investigation_check(), live-verified 2026-10-22 (1,050 rows)</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Same -- a regulator-declared adverse signal.</t>
+          <t>A regulator-declared adverse signal -- genuinely new: /unregProjectList had never been fetched by this pipeline before 2026-10-22 (the 'K-RERA, observed' this row previously said was never backed by an actual fetch). Confirmed live: clean Project Name / Promoter Name / Status / Corporate Address / Published Date columns, Status carrying the authority's own finding per row (e.g. 'No Reply from Promoter'). Covers UNREGISTERED sites only, so a hit is evidence about the promoter, never about an already-registered project.</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -3410,22 +3410,22 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>K-RERA cost incurred vs estimated</t>
+          <t>Maha Bhulekh card fields</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>K-RERA detail page</t>
+          <t>Free portal, now has an OCR fallback for image-only cards</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Karnataka projects</t>
+          <t>Maharashtra projects</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Financial-strength scores None everywhere today. This is a direct, free input.</t>
+          <t>WIRED 2026-10-22: confirmed live that a property with no digitized attribute data on file renders as a single scanned JPEG even with English selected (parse_property_card correctly returns {} on that page -- there is no markup to read, not a parser bug). mahabhumi._fields_from_ocr_text() now OCRs the cropped card image itself (not the noisy full-page screenshot) and extracts labelled fields from the OCR text as `ocr_fields`, kept separate from the DOM-parsed `fields` so a caller can tell a table read from a lower-confidence scan guess. Verified against two real saved captures with digitized cards (full fields/mutations) and one real image-only capture (ocr_fields now the only route in).</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -3437,130 +3437,130 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>K-RERA delay reasons + NOC expiry</t>
+          <t>JHARERA audited balance sheet + 3 years ITR</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>K-RERA detail page</t>
+          <t>adapter_jharkhand.py document library -- WIRED 2026-10-22 via JharkhandAdapter._financial_statements(), same mechanism as GujRERA's row above</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Karnataka projects</t>
+          <t>Jharkhand projects</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Promoter-declared delay reasons and lapsed-NOC tracking; no equivalent elsewhere.</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Same gap as GujRERA's findoc block, same partial close: P&amp;L figures now extracted and cited, score stays None, see the Audited balance sheet / P&amp;L / ITR row above for the full reasoning. One extra live finding here: this project's own document labelled 'Balance Sheet' turned out to actually CONTAIN Statement of Profit &amp; Loss text (a portal mislabel, not a scraping error) -- extracted correctly anyway, since this reads the document's own text, never its label.</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Maha Bhulekh card fields</t>
+          <t>JHARERA rejected + surrendered registration lists</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Free portal, now has an OCR fallback for image-only cards</t>
+          <t>REJECTED_LIST / SURRENDERED_LIST -- WIRED 2026-10-22 via JharkhandAdapter._rejected_or_surrendered_check(), live-verified on wiring (13 rows: 10 rejected + 3 surrendered)</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Maharashtra projects</t>
+          <t>Jharkhand projects</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>WIRED 2026-10-22: confirmed live that a property with no digitized attribute data on file renders as a single scanned JPEG even with English selected (parse_property_card correctly returns {} on that page -- there is no markup to read, not a parser bug). mahabhumi._fields_from_ocr_text() now OCRs the cropped card image itself (not the noisy full-page screenshot) and extracts labelled fields from the OCR text as `ocr_fields`, kept separate from the DOM-parsed `fields` so a caller can tell a table read from a lower-confidence scan guess. Verified against two real saved captures with digitized cards (full fields/mutations) and one real image-only capture (ocr_fields now the only route in).</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>A rejected or surrendered registration is diligence material with no equivalent on MahaRERA. Runs unconditionally on every JHARERA acquire(): two cheap GETs for the whole state's registers, not a per-project cost.</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>JHARERA audited balance sheet + 3 years ITR</t>
+          <t>WBRERA defaulters list</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>adapter_jharkhand.py document library (labelled, downloaded)</t>
+          <t>adapter_westbengal.fetch_defaulters() -- WIRED 2026-10-22 via WestBengalAdapter._defaulter_check(), live-verified on wiring (18 rows)</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Jharkhand projects</t>
+          <t>West Bengal projects</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Same gap as GujRERA's findoc block: the financial-strength sub-metric scores None for every project regardless of state. This would score it for JH too.</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>A cheap, direct red-flag input. CORRECTED ON WIRING 2026-10-22: the register's own 'name' column is the PROJECT's name, not a promoter name -- there is no promoter field on this register at all, confirmed live. So this matches on the resolved project's own name, not promoter_name the way every other defaulter check in this pipeline does, and a hit says nothing about the promoter's other projects.</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>JHARERA rejected + surrendered registration lists</t>
+          <t>UP-RERA de-registered/defaulter list</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>REJECTED_LIST / SURRENDERED_LIST -- WIRED 2026-10-22 via JharkhandAdapter._rejected_or_surrendered_check(), live-verified on wiring (13 rows: 10 rejected + 3 surrendered)</t>
+          <t>adapter_uttarpradesh.fetch_defaulters() -- WIRED 2026-10-22 via UttarPradeshAdapter._defaulter_check(), live-verified 2026-08-26 and again on wiring (72 rows)</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Jharkhand projects</t>
+          <t>Uttar Pradesh projects</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>A rejected or surrendered registration is diligence material with no equivalent on MahaRERA. Runs unconditionally on every JHARERA acquire(): two cheap GETs for the whole state's registers, not a per-project cost.</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Named by promoter outright -- ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED is on it (3 matching rows, re-confirmed live). Runs unconditionally on every UP-RERA acquire(): one homepage GET plus one ASP.NET postback for the whole state's register, not a per-project cost.</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>WBRERA defaulters list</t>
+          <t>HARERA cancelled/defaulter projects</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>adapter_westbengal.fetch_defaulters() -- WIRED 2026-10-22 via WestBengalAdapter._defaulter_check(), live-verified on wiring (18 rows)</t>
+          <t>adapter_haryana.fetch_defaulter_projects() -- WIRED 2026-10-22 via HaryanaAdapter._defaulter_check(), live-verified 2026-08-26 and again on wiring (23 Panchkula + 5 Gurugram)</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>West Bengal projects</t>
+          <t>Haryana projects</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>A cheap, direct red-flag input. CORRECTED ON WIRING 2026-10-22: the register's own 'name' column is the PROJECT's name, not a promoter name -- there is no promoter field on this register at all, confirmed live. So this matches on the resolved project's own name, not promoter_name the way every other defaulter check in this pipeline does, and a hit says nothing about the promoter's other projects.</t>
+          <t>Distinct from the already-imported LAPSED_PROJECTS URL, which is validity expiry, not an authority action -- conflating the two would understate lapsed rows as defaults or vice versa. Only the resolved project's OWN bench is checked per acquire() call; a promoter active on both benches under the same name would need both swept, left to the group-enforcement pass rather than a single-project lookup.</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -3572,49 +3572,49 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>UP-RERA de-registered/defaulter list</t>
+          <t>TNRERA penalty register</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>adapter_uttarpradesh.fetch_defaulters() -- WIRED 2026-10-22 via UttarPradeshAdapter._defaulter_check(), live-verified 2026-08-26 and again on wiring (72 rows)</t>
+          <t>adapter_tamilnadu.fetch_penalty_notices() -- WIRED 2026-10-22 via TamilNaduAdapter._penalty_check(), live-verified 2026-08-26 and again on wiring (146 rows across Building + Layout)</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Uttar Pradesh projects</t>
+          <t>Tamil Nadu projects</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Named by promoter outright -- ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED is on it (3 matching rows, re-confirmed live). Runs unconditionally on every UP-RERA acquire(): one homepage GET plus one ASP.NET postback for the whole state's register, not a per-project cost.</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Names promoter, project and the penalty amount levied -- TNRERA's own closest equivalent to a defaulters list, titled 'Penalty' rather than that. Runs unconditionally: two GETs (Building + Layout) on every TNRERA acquire().</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>HARERA cancelled/defaulter projects</t>
+          <t>TNRERA unregistered-project enforcement PDFs</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>adapter_haryana.fetch_defaulter_projects() -- WIRED 2026-10-22 via HaryanaAdapter._defaulter_check(), live-verified 2026-08-26 and again on wiring (23 Panchkula + 5 Gurugram)</t>
+          <t>adapter_tamilnadu.search_enforcement_lists_by_name() -- WIRED 2026-10-22 via TamilNaduAdapter._enforcement_check(), live-verified 2026-08-26 and again on wiring (35 + 1,502 rows, native-text PDFs, no OCR needed)</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Haryana projects</t>
+          <t>Tamil Nadu projects/promoters</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Distinct from the already-imported LAPSED_PROJECTS URL, which is validity expiry, not an authority action -- conflating the two would understate lapsed rows as defaults or vice versa. Only the resolved project's OWN bench is checked per acquire() call; a promoter active on both benches under the same name would need both swept, left to the group-enforcement pass rather than a single-project lookup.</t>
+          <t>The show-cause and personal-use-caution lists, now actually searchable by name rather than merely linked as static PDFs. Ceiling is real, not fixable in code: both cover UNREGISTERED sites, never a registered project under suo-moto scrutiny, so a hit is evidence about the PROMOTER, not this project. Runs unconditionally, though the personal-use caution PDF is 118 pages and noticeably slower than every other per-promoter check in this adapter.</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -3626,49 +3626,49 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>TNRERA penalty register</t>
+          <t>Delhi-RERA suo-moto register</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>adapter_tamilnadu.fetch_penalty_notices() -- WIRED 2026-10-22 via TamilNaduAdapter._penalty_check(), live-verified 2026-08-26 and again on wiring (146 rows across Building + Layout)</t>
+          <t>adapter_delhi.parse_suo_moto_register() -- WIRED 2026-10-22 via DelhiAdapter._suo_moto(), live-verified 2026-08-26 and again on wiring (1,781 rows)</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Tamil Nadu projects</t>
+          <t>Delhi projects</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Names promoter, project and the penalty amount levied -- TNRERA's own closest equivalent to a defaulters list, titled 'Penalty' rather than that. Runs unconditionally: two GETs (Building + Layout) on every TNRERA acquire().</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Names a Respondent/Promoter and project per row -- the clearest 'projects under investigation' signal found on any of the four newest states, and Delhi otherwise has no per-project record at all. Runs unconditionally: one GET for the whole register, same cost shape as the complaint register sweep already in this adapter. Surfaced as category_data['suo_moto_investigations']; not yet mapped to a Charter facts field (still '(unmapped)' in Sheet A).</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>TNRERA unregistered-project enforcement PDFs</t>
+          <t>Delhi-RERA execution register</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>adapter_tamilnadu.search_enforcement_lists_by_name() -- WIRED 2026-10-22 via TamilNaduAdapter._enforcement_check(), live-verified 2026-08-26 and again on wiring (35 + 1,502 rows, native-text PDFs, no OCR needed)</t>
+          <t>adapter_delhi.parse_execution_register() -- WIRED 2026-10-22 via DelhiAdapter._execution_register(), live-verified 2026-08-26 and again on wiring (5,921 rows)</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Tamil Nadu projects/promoters</t>
+          <t>Delhi projects</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>The show-cause and personal-use-caution lists, now actually searchable by name rather than merely linked as static PDFs. Ceiling is real, not fixable in code: both cover UNREGISTERED sites, never a registered project under suo-moto scrutiny, so a hit is evidence about the PROMOTER, not this project. Runs unconditionally, though the personal-use caution PDF is 118 pages and noticeably slower than every other per-promoter check in this adapter.</t>
+          <t>Orders referred for enforcement because the promoter (named as Judgement Debtor) did not comply -- the authority's own closest equivalent to a defaulters list. Runs unconditionally: one GET for the whole register.</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -3680,12 +3680,12 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Delhi-RERA suo-moto register</t>
+          <t>Delhi-RERA Appellate Tribunal (REAT) register, WITH party names</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>adapter_delhi.parse_suo_moto_register() -- WIRED 2026-10-22 via DelhiAdapter._suo_moto(), live-verified 2026-08-26 and again on wiring (1,781 rows)</t>
+          <t>adapter_delhi.build_appeal_party_index() / search_appeals_by_party() -- WIRED 2026-10-22 via DelhiAdapter._reat_appeals(), live-verified 2026-08-26 (437/505 rows named, 481 PDFs OCR'd)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Names a Respondent/Promoter and project per row -- the clearest 'projects under investigation' signal found on any of the four newest states, and Delhi otherwise has no per-project record at all. Runs unconditionally: one GET for the whole register, same cost shape as the complaint register sweep already in this adapter. Surfaced as category_data['suo_moto_investigations']; not yet mapped to a Charter facts field (still '(unmapped)' in Sheet A).</t>
+          <t>The register itself names no party -- not linked from any Delhi-RERA page either, found only by web search -- but every row links a scanned judgement PDF whose own case caption does. OCRing just the PDFs' first pages (PyMuPDF native text, confirmed zero on every sample -- Tesseract fallback) turned an unsearchable register into one where search_appeals_by_party('Parsvnath') returns 27 real hits. The only gaps are the authority's own 63 broken PDF links and 5 older (2021-2022) PDFs in a caption shape not yet recognised. OFF BY DEFAULT even though wired: 481 PDFs is too expensive to fetch+OCR on every Delhi-RERA acquire() call, so it only runs with DELHI_REAT_SWEEP=1, caching each PDF's OCR text to &lt;output_dir&gt;/_reat_pdf_cache so a repeat sweep only pays for PDFs not seen before. A run without the flag set gets an explicit 'not swept' note, never a silent clean record.</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -3704,62 +3704,8 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Delhi-RERA execution register</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>adapter_delhi.parse_execution_register() -- WIRED 2026-10-22 via DelhiAdapter._execution_register(), live-verified 2026-08-26 and again on wiring (5,921 rows)</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Delhi projects</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Orders referred for enforcement because the promoter (named as Judgement Debtor) did not comply -- the authority's own closest equivalent to a defaulters list. Runs unconditionally: one GET for the whole register.</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Delhi-RERA Appellate Tribunal (REAT) register, WITH party names</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>adapter_delhi.build_appeal_party_index() / search_appeals_by_party() -- WIRED 2026-10-22 via DelhiAdapter._reat_appeals(), live-verified 2026-08-26 (437/505 rows named, 481 PDFs OCR'd)</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Delhi projects</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>The register itself names no party -- not linked from any Delhi-RERA page either, found only by web search -- but every row links a scanned judgement PDF whose own case caption does. OCRing just the PDFs' first pages (PyMuPDF native text, confirmed zero on every sample -- Tesseract fallback) turned an unsearchable register into one where search_appeals_by_party('Parsvnath') returns 27 real hits. The only gaps are the authority's own 63 broken PDF links and 5 older (2021-2022) PDFs in a caption shape not yet recognised. OFF BY DEFAULT even though wired: 481 PDFs is too expensive to fetch+OCR on every Delhi-RERA acquire() call, so it only runs with DELHI_REAT_SWEEP=1, caching each PDF's OCR text to &lt;output_dir&gt;/_reat_pdf_cache so a repeat sweep only pays for PDFs not seen before. A run without the flag set gets an explicit 'not swept' note, never a silent clean record.</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:E21"/>
+  <autoFilter ref="A4:E19"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A - RERA by authority'!$A$4:$M$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B - CTS land records'!$A$4:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B - CTS land records'!$A$4:$F$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C - CIN corporate'!$A$4:$G$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D - Available but unused'!$A$4:$E$19</definedName>
   </definedNames>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regenerated 2026-10-22 by build_data_coverage.py</t>
+          <t>Regenerated 2026-10-26 by build_data_coverage.py</t>
         </is>
       </c>
     </row>
@@ -736,6 +736,13 @@
       <c r="A35" s="3" t="inlineStr">
         <is>
           <t>19. CAPTCHA autosolve went pipeline-wide 2026-10-15, Claude-vision-only. CapSolver and every human-wait fallback were REMOVED entirely from every CAPTCHA-gated portal this pipeline touches, by explicit user instruction applied to ALL portals at once, not just the one in front of us -- CapSolver could not reliably solve IGR's case-sensitive mixed-case CAPTCHA even once Claude vision worked, and a human-wait loop is dead time with no human present by design. Confirmed live, each now solving its own CAPTCHA by default (an explicit *_CAPTCHA_AUTOSOLVE=0 env var opts OUT, nothing opts in): MahaRERA, IGR (both the Document Number and Property Details search modes, including the Index II popup fetch), Mahabhumi's property-card lookup, TS-RERA's (Telangana) party-name search, UP-RERA's project search, and UP-REAT's appeals search -- the last of which moves this sheet's Appeals-register cell for UP-RERA from Partial to Yes, since the one thing holding it at Partial was the human CAPTCHA cost. GST (PAN-&gt;GSTIN intake) autosolve code is ready but not fully proven -- the portal was WAF-blocked during testing and live verification was explicitly deferred. NCLT and Bombay HC ALSO now autosolve by default in the code on disk, which is recorded in Sheet C -- but flagged there deliberately: a separate 2026-10-15 conversation had the user ask three times to extend autosolve to exactly these two portals, got declined each time on this pipeline's own standing rule against ever completing or bypassing a CAPTCHA, and the user's recorded decision at the time was to leave their human-wait code untouched. The code and CLAUDE.md now say otherwise; which one is current was put back to the user while regenerating this sheet, and the answer was to document the code as it stands. Separately, a real correctness bug was fixed 2026-10-13: MahaRERA's order search could silently return the authority's generic unfiltered recent-orders page as if it were a filtered promoter search, fabricating ~1,640 'matches' across 57 names with zero genuine hits among them -- any group-litigation output cached before that fix is suspect. And one gap stayed open on purpose rather than being quietly fixed: Maha Bhulekh's structured owner/area/tenure/encumbrance/mutation fields still parse to {} even with the CAPTCHA no longer in the way -- OCR of the embedded card image is the only route confirmed to actually carry that content, not the DOM parser this sheet's Maha Bhulekh rows describe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>20. 2026-10-26: GR Maharashtra's GR-citation lookup (Sheet B, new row) gained Claude-vision autosolve, the same day the per-finding Charter research pass was parallelized (8 findings now run concurrently instead of sequentially, same per-finding failure isolation) and the shared Claude API client gained an explicit request timeout (connect=10s/read=90s/write=30s/pool=10s) after a transport call hung with no bound in this sandbox -- every [never fatal] stage that funnels through _run_agentic_pass now fails within a bounded window on a stalled connection instead of risking an indefinite hang. GST was explicitly reverted to human-by-default at the user's request (the one deliberate exception to the pipeline-wide autosolve policy in entry 19 above) -- the autosolve code is untouched and still reachable via autosolve=True/GST_CAPTCHA_AUTOSOLVE=1, it is simply no longer the default; entry 19's own 'not fully proven, WAF-blocked' framing is superseded by this deliberate choice, not resolved by it. Haryana's two CAPTCHA-gated endpoints (project search, case/complaint search) were attempted but NOT built: haryanarera.gov.in was unreachable from this session's browser across seven independent checks (https/http, two tabs, three paths, and a raw fetch from the sibling hareraggm.gov.in domain, which loaded fine) -- no selector or CAPTCHA mechanism was ever actually observed, so nothing was written against a guess.</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2713,8 +2720,40 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Government Resolution (GR) file-number citation lookup</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Maharashtra GR portal (gr.maharashtra.gov.in)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Free + CAPTCHA (autosolved)</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>confirmed-live</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>NEW ROW 2026-10-26 -- gr_maharashtra_search.py, a genuinely separate workflow from Mahabhumi's CTS/Property-Card lookup above: a project's land/title documents sometimes cite a reference that LOOKS like a CTS/survey number but is actually a Government Resolution file number (Marathi convention "&lt;dept-code&gt;-&lt;serial&gt;/CR-&lt;serial&gt;/&lt;dept-abbrev&gt;-&lt;serial&gt;", e.g. "CID-1812/CR-274/UD-10") -- a policy document, not a land parcel, and Mahabhumi's own search will never resolve it. company_charter.run_cts_land_lookup() detects the shape (_looks_like_gr_citation) and routes to this portal instead. CONFIRMED LIVE 2026-08/09 against a real Navi Mumbai CIDCO resettlement-scheme GR: Department + date range found the actual published text. CLAUDE-VISION AUTOSOLVE ADDED 2026-10-26 (captcha_solver.solve_gr_captcha), replacing the original human-wait design -- the one genuinely tricky part: this portal gives NO rejection text on a wrong CAPTCHA at all (confirmed live by deliberately submitting a wrong answer twice), and the default unfiltered recent-GRs listing renders inside the exact same #SitePH_dgvDocuments table a real result would, so table-presence alone can't tell them apart. The retry loop instead tracks #SitePH_ucPaging_lblTotalRecords (the total-record count) against its pre-submit baseline and only accepts a result once that count moves or the confirmed-empty 'माहिती उपलब्ध नाही' marker appears.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F16"/>
+  <autoFilter ref="A4:F17"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
